--- a/data/processed/positivacao/2026-01_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2026-01_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26661,7 +26661,7 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr"/>
@@ -37831,7 +37831,7 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr"/>
@@ -65917,7 +65917,7 @@
     <row r="2524">
       <c r="A2524" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2524" t="inlineStr"/>
@@ -67510,12 +67510,12 @@
       <c r="A2586" t="inlineStr"/>
       <c r="B2586" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 6 cliente(s), não positivou 83 cliente(s) - Total vendido: R$ 3.006,37
+          <t>Vendedor 1 - VENDEDOR 01: positivou 6 cliente(s), não positivou 83 cliente(s) - Total vendido: R$ 3.006,37
 Vendedor 18 - LOJA: positivou 252 cliente(s), não positivou 662 cliente(s) - Total vendido: R$ 79.240,32
-Vendedor 3 - FERNANDA: positivou 115 cliente(s), não positivou 314 cliente(s) - Total vendido: R$ 155.573,11
-Vendedor 4 - DANIELA: positivou 111 cliente(s), não positivou 524 cliente(s) - Total vendido: R$ 83.713,75
+Vendedor 3 - VENDEDOR 03: positivou 115 cliente(s), não positivou 314 cliente(s) - Total vendido: R$ 155.573,11
+Vendedor 4 - VENDEDOR 04: positivou 111 cliente(s), não positivou 524 cliente(s) - Total vendido: R$ 83.713,75
 Vendedor 5 - SITE: positivou 1 cliente(s), não positivou 443 cliente(s) - Total vendido: R$ 215,07
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2586" t="inlineStr"/>
